--- a/showroom.xlsx
+++ b/showroom.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axel\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axel\Desktop\INVENTARIO CAT 1, CAT4 Y SHOWROOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D1EFBB-B5CC-41A5-B5C9-A5C65ADFD3CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B04C56-89E2-4F8C-AA6B-8C96C2A8AAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CF10072B-5FA1-483C-94D3-1D39B98166AE}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'TRAJE BASICO'!$A$1:$C$73</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TUXEDOS!$A$1:$C$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">TUXEDOS!$A$1:$C$32</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="107">
   <si>
     <t>CANTIDAD</t>
   </si>
@@ -360,6 +360,9 @@
   </si>
   <si>
     <t>DESCRIPCION</t>
+  </si>
+  <si>
+    <t>TRAJE 40R BL301-08</t>
   </si>
 </sst>
 </file>
@@ -770,10 +773,10 @@
   <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -1524,12 +1527,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5811CC63-BFA7-4CFB-89A6-6690CDDFAF48}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="50.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1590,7 +1593,7 @@
     <row r="6" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>4</v>
+        <v>106</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1600,7 +1603,7 @@
     <row r="7" spans="1:4">
       <c r="A7" s="2"/>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C7" s="3">
         <v>1</v>
@@ -1610,7 +1613,7 @@
     <row r="8" spans="1:4">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1620,7 +1623,7 @@
     <row r="9" spans="1:4">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -1630,7 +1633,7 @@
     <row r="10" spans="1:4">
       <c r="A10" s="2"/>
       <c r="B10" s="2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3">
         <v>1</v>
@@ -1640,7 +1643,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -1650,7 +1653,7 @@
     <row r="12" spans="1:4">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1660,7 +1663,7 @@
     <row r="13" spans="1:4">
       <c r="A13" s="2"/>
       <c r="B13" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C13" s="3">
         <v>1</v>
@@ -1670,7 +1673,7 @@
     <row r="14" spans="1:4">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1680,7 +1683,7 @@
     <row r="15" spans="1:4">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -1690,7 +1693,7 @@
     <row r="16" spans="1:4">
       <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3">
         <v>1</v>
@@ -1700,7 +1703,7 @@
     <row r="17" spans="1:4">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -1710,7 +1713,7 @@
     <row r="18" spans="1:4">
       <c r="A18" s="2"/>
       <c r="B18" s="2" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="C18" s="3">
         <v>1</v>
@@ -1720,7 +1723,7 @@
     <row r="19" spans="1:4">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" s="3">
         <v>1</v>
@@ -1730,7 +1733,7 @@
     <row r="20" spans="1:4">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -1740,7 +1743,7 @@
     <row r="21" spans="1:4">
       <c r="A21" s="2"/>
       <c r="B21" s="2" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C21" s="3">
         <v>1</v>
@@ -1750,7 +1753,7 @@
     <row r="22" spans="1:4">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -1760,7 +1763,7 @@
     <row r="23" spans="1:4">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -1770,7 +1773,7 @@
     <row r="24" spans="1:4">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -1780,7 +1783,7 @@
     <row r="25" spans="1:4">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
@@ -1790,7 +1793,7 @@
     <row r="26" spans="1:4">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C26" s="3">
         <v>1</v>
@@ -1800,7 +1803,7 @@
     <row r="27" spans="1:4">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
@@ -1810,7 +1813,7 @@
     <row r="28" spans="1:4">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -1820,7 +1823,7 @@
     <row r="29" spans="1:4">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="3">
         <v>1</v>
@@ -1830,7 +1833,7 @@
     <row r="30" spans="1:4">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -1840,18 +1843,28 @@
     <row r="31" spans="1:4">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="3">
+        <v>1</v>
+      </c>
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C31" s="3">
-        <v>1</v>
-      </c>
-      <c r="D31" s="1"/>
+      <c r="C32" s="3">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C31" xr:uid="{5811CC63-BFA7-4CFB-89A6-6690CDDFAF48}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X31">
-    <sortCondition ref="W2:W31"/>
-    <sortCondition ref="X2:X31"/>
+  <autoFilter ref="A1:C32" xr:uid="{5811CC63-BFA7-4CFB-89A6-6690CDDFAF48}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X32">
+    <sortCondition ref="W2:W32"/>
+    <sortCondition ref="X2:X32"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/showroom.xlsx
+++ b/showroom.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\axel\Desktop\INVENTARIO CAT 1, CAT4 Y SHOWROOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24B04C56-89E2-4F8C-AA6B-8C96C2A8AAFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A29450-3632-49DC-9E51-900BD094E2BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{CF10072B-5FA1-483C-94D3-1D39B98166AE}"/>
   </bookViews>
@@ -71,9 +71,6 @@
     <t xml:space="preserve">TRAJE 40R G47815-1 OSCAR CHALECO NEGRO </t>
   </si>
   <si>
-    <t xml:space="preserve">TRAJE 42R G47815-17OSCAR CHALECO AZUL </t>
-  </si>
-  <si>
     <t xml:space="preserve">TRAJE 44R  C67901-1 SLIM NEGRO </t>
   </si>
   <si>
@@ -363,6 +360,9 @@
   </si>
   <si>
     <t>TRAJE 40R BL301-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRAJE 42R G47815-17 OSCAR CHALECO AZUL </t>
   </si>
 </sst>
 </file>
@@ -781,10 +781,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>0</v>
@@ -796,7 +796,7 @@
     <row r="2" spans="1:4" ht="15">
       <c r="A2" s="2"/>
       <c r="B2" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" s="7">
         <v>1</v>
@@ -806,7 +806,7 @@
     <row r="3" spans="1:4" ht="15">
       <c r="A3" s="2"/>
       <c r="B3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
@@ -816,7 +816,7 @@
     <row r="4" spans="1:4" ht="15">
       <c r="A4" s="2"/>
       <c r="B4" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
@@ -826,7 +826,7 @@
     <row r="5" spans="1:4" ht="15">
       <c r="A5" s="2"/>
       <c r="B5" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
@@ -836,7 +836,7 @@
     <row r="6" spans="1:4" ht="15">
       <c r="A6" s="2"/>
       <c r="B6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
@@ -846,7 +846,7 @@
     <row r="7" spans="1:4" ht="15">
       <c r="A7" s="2"/>
       <c r="B7" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
@@ -856,7 +856,7 @@
     <row r="8" spans="1:4" ht="15">
       <c r="A8" s="2"/>
       <c r="B8" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
@@ -866,7 +866,7 @@
     <row r="9" spans="1:4" ht="15">
       <c r="A9" s="2"/>
       <c r="B9" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="7">
         <v>1</v>
@@ -876,7 +876,7 @@
     <row r="10" spans="1:4" ht="15">
       <c r="A10" s="2"/>
       <c r="B10" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C10" s="7">
         <v>1</v>
@@ -886,7 +886,7 @@
     <row r="11" spans="1:4" ht="15">
       <c r="A11" s="2"/>
       <c r="B11" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -896,7 +896,7 @@
     <row r="12" spans="1:4" ht="15">
       <c r="A12" s="2"/>
       <c r="B12" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
@@ -906,7 +906,7 @@
     <row r="13" spans="1:4" ht="15">
       <c r="A13" s="2"/>
       <c r="B13" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
@@ -916,7 +916,7 @@
     <row r="14" spans="1:4" ht="15">
       <c r="A14" s="2"/>
       <c r="B14" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C14" s="7">
         <v>1</v>
@@ -926,7 +926,7 @@
     <row r="15" spans="1:4" ht="15">
       <c r="A15" s="2"/>
       <c r="B15" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
@@ -936,7 +936,7 @@
     <row r="16" spans="1:4" ht="15">
       <c r="A16" s="2"/>
       <c r="B16" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C16" s="7">
         <v>1</v>
@@ -946,7 +946,7 @@
     <row r="17" spans="1:4" ht="15">
       <c r="A17" s="2"/>
       <c r="B17" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C17" s="7">
         <v>1</v>
@@ -956,7 +956,7 @@
     <row r="18" spans="1:4" ht="15">
       <c r="A18" s="2"/>
       <c r="B18" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
@@ -966,7 +966,7 @@
     <row r="19" spans="1:4" ht="15">
       <c r="A19" s="2"/>
       <c r="B19" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="7">
         <v>1</v>
@@ -976,7 +976,7 @@
     <row r="20" spans="1:4" ht="15">
       <c r="A20" s="2"/>
       <c r="B20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="7">
         <v>2</v>
@@ -986,7 +986,7 @@
     <row r="21" spans="1:4" ht="15">
       <c r="A21" s="2"/>
       <c r="B21" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C21" s="7">
         <v>1</v>
@@ -996,7 +996,7 @@
     <row r="22" spans="1:4" ht="15">
       <c r="A22" s="2"/>
       <c r="B22" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C22" s="7">
         <v>1</v>
@@ -1006,7 +1006,7 @@
     <row r="23" spans="1:4" ht="15">
       <c r="A23" s="2"/>
       <c r="B23" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
@@ -1016,7 +1016,7 @@
     <row r="24" spans="1:4" ht="15">
       <c r="A24" s="2"/>
       <c r="B24" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C24" s="7">
         <v>1</v>
@@ -1026,7 +1026,7 @@
     <row r="25" spans="1:4" ht="15">
       <c r="A25" s="2"/>
       <c r="B25" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C25" s="7">
         <v>1</v>
@@ -1036,7 +1036,7 @@
     <row r="26" spans="1:4" ht="15">
       <c r="A26" s="2"/>
       <c r="B26" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C26" s="7">
         <v>1</v>
@@ -1046,7 +1046,7 @@
     <row r="27" spans="1:4" ht="15">
       <c r="A27" s="2"/>
       <c r="B27" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C27" s="7">
         <v>1</v>
@@ -1056,7 +1056,7 @@
     <row r="28" spans="1:4" ht="15">
       <c r="A28" s="2"/>
       <c r="B28" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="7">
         <v>1</v>
@@ -1066,7 +1066,7 @@
     <row r="29" spans="1:4" ht="15">
       <c r="A29" s="2"/>
       <c r="B29" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C29" s="7">
         <v>1</v>
@@ -1076,7 +1076,7 @@
     <row r="30" spans="1:4" ht="15">
       <c r="A30" s="2"/>
       <c r="B30" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C30" s="7">
         <v>1</v>
@@ -1086,7 +1086,7 @@
     <row r="31" spans="1:4" ht="15">
       <c r="A31" s="2"/>
       <c r="B31" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="7">
         <v>1</v>
@@ -1096,7 +1096,7 @@
     <row r="32" spans="1:4" ht="15">
       <c r="A32" s="2"/>
       <c r="B32" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C32" s="7">
         <v>1</v>
@@ -1106,7 +1106,7 @@
     <row r="33" spans="1:4" ht="15">
       <c r="A33" s="2"/>
       <c r="B33" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C33" s="7">
         <v>2</v>
@@ -1116,7 +1116,7 @@
     <row r="34" spans="1:4" ht="15">
       <c r="A34" s="2"/>
       <c r="B34" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C34" s="7">
         <v>1</v>
@@ -1126,7 +1126,7 @@
     <row r="35" spans="1:4" ht="15">
       <c r="A35" s="2"/>
       <c r="B35" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -1136,7 +1136,7 @@
     <row r="36" spans="1:4" ht="15">
       <c r="A36" s="2"/>
       <c r="B36" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C36" s="7">
         <v>1</v>
@@ -1146,7 +1146,7 @@
     <row r="37" spans="1:4" ht="15">
       <c r="A37" s="2"/>
       <c r="B37" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C37" s="7">
         <v>1</v>
@@ -1156,7 +1156,7 @@
     <row r="38" spans="1:4" ht="15">
       <c r="A38" s="2"/>
       <c r="B38" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" s="7">
         <v>1</v>
@@ -1166,7 +1166,7 @@
     <row r="39" spans="1:4" ht="15">
       <c r="A39" s="2"/>
       <c r="B39" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C39" s="7">
         <v>1</v>
@@ -1176,7 +1176,7 @@
     <row r="40" spans="1:4" ht="15">
       <c r="A40" s="2"/>
       <c r="B40" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C40" s="7">
         <v>1</v>
@@ -1186,7 +1186,7 @@
     <row r="41" spans="1:4" ht="15">
       <c r="A41" s="2"/>
       <c r="B41" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" s="7">
         <v>1</v>
@@ -1196,7 +1196,7 @@
     <row r="42" spans="1:4" ht="15">
       <c r="A42" s="2"/>
       <c r="B42" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C42" s="7">
         <v>1</v>
@@ -1206,7 +1206,7 @@
     <row r="43" spans="1:4" ht="15">
       <c r="A43" s="2"/>
       <c r="B43" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -1216,7 +1216,7 @@
     <row r="44" spans="1:4" ht="15">
       <c r="A44" s="2"/>
       <c r="B44" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C44" s="7">
         <v>1</v>
@@ -1226,7 +1226,7 @@
     <row r="45" spans="1:4" ht="15">
       <c r="A45" s="2"/>
       <c r="B45" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" s="7">
         <v>1</v>
@@ -1236,7 +1236,7 @@
     <row r="46" spans="1:4" ht="15">
       <c r="A46" s="2"/>
       <c r="B46" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C46" s="7">
         <v>1</v>
@@ -1246,7 +1246,7 @@
     <row r="47" spans="1:4" ht="15">
       <c r="A47" s="2"/>
       <c r="B47" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C47" s="7">
         <v>1</v>
@@ -1256,7 +1256,7 @@
     <row r="48" spans="1:4" ht="15">
       <c r="A48" s="2"/>
       <c r="B48" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C48" s="7">
         <v>1</v>
@@ -1266,7 +1266,7 @@
     <row r="49" spans="1:4" ht="15">
       <c r="A49" s="2"/>
       <c r="B49" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C49" s="7">
         <v>1</v>
@@ -1276,7 +1276,7 @@
     <row r="50" spans="1:4" ht="15">
       <c r="A50" s="2"/>
       <c r="B50" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50" s="7">
         <v>1</v>
@@ -1286,7 +1286,7 @@
     <row r="51" spans="1:4" ht="15">
       <c r="A51" s="2"/>
       <c r="B51" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C51" s="7">
         <v>1</v>
@@ -1296,7 +1296,7 @@
     <row r="52" spans="1:4" ht="15">
       <c r="A52" s="2"/>
       <c r="B52" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C52" s="7">
         <v>1</v>
@@ -1306,7 +1306,7 @@
     <row r="53" spans="1:4" ht="15">
       <c r="A53" s="2"/>
       <c r="B53" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C53" s="7">
         <v>1</v>
@@ -1316,7 +1316,7 @@
     <row r="54" spans="1:4" ht="15">
       <c r="A54" s="2"/>
       <c r="B54" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C54" s="7">
         <v>1</v>
@@ -1326,7 +1326,7 @@
     <row r="55" spans="1:4" ht="15">
       <c r="A55" s="2"/>
       <c r="B55" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C55" s="7">
         <v>1</v>
@@ -1336,7 +1336,7 @@
     <row r="56" spans="1:4" ht="15">
       <c r="A56" s="2"/>
       <c r="B56" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C56" s="7">
         <v>1</v>
@@ -1346,7 +1346,7 @@
     <row r="57" spans="1:4" ht="15">
       <c r="A57" s="2"/>
       <c r="B57" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C57" s="7">
         <v>1</v>
@@ -1356,7 +1356,7 @@
     <row r="58" spans="1:4" ht="15">
       <c r="A58" s="2"/>
       <c r="B58" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C58" s="7">
         <v>1</v>
@@ -1366,7 +1366,7 @@
     <row r="59" spans="1:4" ht="15">
       <c r="A59" s="2"/>
       <c r="B59" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C59" s="7">
         <v>1</v>
@@ -1376,7 +1376,7 @@
     <row r="60" spans="1:4" ht="15">
       <c r="A60" s="2"/>
       <c r="B60" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C60" s="7">
         <v>1</v>
@@ -1386,7 +1386,7 @@
     <row r="61" spans="1:4" ht="15">
       <c r="A61" s="2"/>
       <c r="B61" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C61" s="7">
         <v>1</v>
@@ -1396,7 +1396,7 @@
     <row r="62" spans="1:4" ht="15">
       <c r="A62" s="2"/>
       <c r="B62" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C62" s="7">
         <v>1</v>
@@ -1406,7 +1406,7 @@
     <row r="63" spans="1:4" ht="15">
       <c r="A63" s="2"/>
       <c r="B63" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C63" s="7">
         <v>1</v>
@@ -1416,7 +1416,7 @@
     <row r="64" spans="1:4" ht="15">
       <c r="A64" s="2"/>
       <c r="B64" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C64" s="7">
         <v>1</v>
@@ -1426,7 +1426,7 @@
     <row r="65" spans="1:4" ht="15">
       <c r="A65" s="2"/>
       <c r="B65" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C65" s="7">
         <v>1</v>
@@ -1436,7 +1436,7 @@
     <row r="66" spans="1:4" ht="15">
       <c r="A66" s="2"/>
       <c r="B66" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C66" s="7">
         <v>1</v>
@@ -1446,7 +1446,7 @@
     <row r="67" spans="1:4" ht="15">
       <c r="A67" s="2"/>
       <c r="B67" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C67" s="7">
         <v>1</v>
@@ -1456,7 +1456,7 @@
     <row r="68" spans="1:4" ht="15">
       <c r="A68" s="2"/>
       <c r="B68" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C68" s="7">
         <v>1</v>
@@ -1466,7 +1466,7 @@
     <row r="69" spans="1:4" ht="15">
       <c r="A69" s="2"/>
       <c r="B69" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C69" s="7">
         <v>1</v>
@@ -1476,7 +1476,7 @@
     <row r="70" spans="1:4" ht="15">
       <c r="A70" s="2"/>
       <c r="B70" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C70" s="7">
         <v>1</v>
@@ -1486,7 +1486,7 @@
     <row r="71" spans="1:4" ht="15">
       <c r="A71" s="2"/>
       <c r="B71" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C71" s="7">
         <v>1</v>
@@ -1496,7 +1496,7 @@
     <row r="72" spans="1:4" ht="15">
       <c r="A72" s="2"/>
       <c r="B72" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C72" s="7">
         <v>1</v>
@@ -1506,7 +1506,7 @@
     <row r="73" spans="1:4" ht="15">
       <c r="A73" s="2"/>
       <c r="B73" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C73" s="7">
         <v>1</v>
@@ -1538,10 +1538,10 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B1" t="s">
         <v>104</v>
-      </c>
-      <c r="B1" t="s">
-        <v>105</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -1553,7 +1553,7 @@
     <row r="2" spans="1:4">
       <c r="A2" s="2"/>
       <c r="B2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C2" s="3">
         <v>1</v>
@@ -1563,7 +1563,7 @@
     <row r="3" spans="1:4">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3">
         <v>1</v>
@@ -1573,7 +1573,7 @@
     <row r="4" spans="1:4">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3">
         <v>1</v>
@@ -1583,7 +1583,7 @@
     <row r="5" spans="1:4">
       <c r="A5" s="2"/>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3">
         <v>1</v>
@@ -1593,7 +1593,7 @@
     <row r="6" spans="1:4">
       <c r="A6" s="2"/>
       <c r="B6" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C6" s="3">
         <v>1</v>
@@ -1613,7 +1613,7 @@
     <row r="8" spans="1:4">
       <c r="A8" s="2"/>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" s="3">
         <v>1</v>
@@ -1623,7 +1623,7 @@
     <row r="9" spans="1:4">
       <c r="A9" s="2"/>
       <c r="B9" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3">
         <v>1</v>
@@ -1643,7 +1643,7 @@
     <row r="11" spans="1:4">
       <c r="A11" s="2"/>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3">
         <v>1</v>
@@ -1653,7 +1653,7 @@
     <row r="12" spans="1:4">
       <c r="A12" s="2"/>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3">
         <v>1</v>
@@ -1673,7 +1673,7 @@
     <row r="14" spans="1:4">
       <c r="A14" s="2"/>
       <c r="B14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3">
         <v>1</v>
@@ -1683,7 +1683,7 @@
     <row r="15" spans="1:4">
       <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C15" s="3">
         <v>1</v>
@@ -1703,7 +1703,7 @@
     <row r="17" spans="1:4">
       <c r="A17" s="2"/>
       <c r="B17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C17" s="3">
         <v>1</v>
@@ -1723,7 +1723,7 @@
     <row r="19" spans="1:4">
       <c r="A19" s="2"/>
       <c r="B19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3">
         <v>1</v>
@@ -1733,7 +1733,7 @@
     <row r="20" spans="1:4">
       <c r="A20" s="2"/>
       <c r="B20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C20" s="3">
         <v>1</v>
@@ -1753,7 +1753,7 @@
     <row r="22" spans="1:4">
       <c r="A22" s="2"/>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>106</v>
       </c>
       <c r="C22" s="3">
         <v>1</v>
@@ -1763,7 +1763,7 @@
     <row r="23" spans="1:4">
       <c r="A23" s="2"/>
       <c r="B23" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C23" s="3">
         <v>1</v>
@@ -1773,7 +1773,7 @@
     <row r="24" spans="1:4">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C24" s="3">
         <v>1</v>
@@ -1783,7 +1783,7 @@
     <row r="25" spans="1:4">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25" s="3">
         <v>1</v>
@@ -1803,7 +1803,7 @@
     <row r="27" spans="1:4">
       <c r="A27" s="2"/>
       <c r="B27" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="3">
         <v>1</v>
@@ -1813,7 +1813,7 @@
     <row r="28" spans="1:4">
       <c r="A28" s="2"/>
       <c r="B28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C28" s="3">
         <v>1</v>
@@ -1823,7 +1823,7 @@
     <row r="29" spans="1:4">
       <c r="A29" s="2"/>
       <c r="B29" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C29" s="3">
         <v>1</v>
@@ -1833,7 +1833,7 @@
     <row r="30" spans="1:4">
       <c r="A30" s="2"/>
       <c r="B30" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="3">
         <v>1</v>
@@ -1843,7 +1843,7 @@
     <row r="31" spans="1:4">
       <c r="A31" s="2"/>
       <c r="B31" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" s="3">
         <v>1</v>
@@ -1853,7 +1853,7 @@
     <row r="32" spans="1:4">
       <c r="A32" s="2"/>
       <c r="B32" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C32" s="3">
         <v>1</v>
